--- a/doc/内部培训平台需求-20260302.xlsx
+++ b/doc/内部培训平台需求-20260302.xlsx
@@ -1,15 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12100"/>
+    <workbookView windowHeight="14605"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -177,12 +190,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <charset val="134"/>
-      </rPr>
       <t>负责系统运维、基础数据配置（如</t>
     </r>
     <r>
@@ -1588,12 +1595,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
       <t xml:space="preserve">• </t>
     </r>
     <r>
@@ -1867,6 +1868,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="16"/>
       <name val="仿宋"/>
       <charset val="134"/>
@@ -1889,13 +1897,6 @@
       <sz val="16"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -2547,7 +2548,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2559,20 +2563,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3100,25 +3101,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="19.5384615384615" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.3173076923077" style="1" customWidth="1"/>
-    <col min="3" max="3" width="103.634615384615" style="1" customWidth="1"/>
-    <col min="4" max="4" width="58.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="46.5480769230769" style="1" customWidth="1"/>
-    <col min="6" max="6" width="48.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5405405405405" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.3153153153153" style="1" customWidth="1"/>
+    <col min="3" max="3" width="103.630630630631" style="1" customWidth="1"/>
+    <col min="4" max="4" width="58.7477477477477" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.5495495495495" style="1" customWidth="1"/>
+    <col min="6" max="6" width="48.8738738738739" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="58" customHeight="1" spans="1:3">
+    <row r="1" ht="58" customHeight="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" ht="58" customHeight="1" spans="1:3">
+    <row r="2" ht="58" customHeight="1" spans="1:6">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -3129,7 +3130,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="46" customHeight="1" spans="1:3">
+    <row r="3" ht="46" customHeight="1" spans="1:6">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -3151,7 +3152,7 @@
       <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -3163,14 +3164,14 @@
       <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="46" customHeight="1" spans="1:4">
+    <row r="6" ht="46" customHeight="1" spans="1:6">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
@@ -3184,7 +3185,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" ht="46" customHeight="1" spans="1:4">
+    <row r="7" ht="46" customHeight="1" spans="1:6">
       <c r="A7" s="4"/>
       <c r="B7" s="5" t="s">
         <v>19</v>
@@ -3192,11 +3193,11 @@
       <c r="C7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="46" customHeight="1" spans="1:5">
+    <row r="8" ht="46" customHeight="1" spans="1:6">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
         <v>22</v>
@@ -3207,11 +3208,11 @@
       <c r="D8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" ht="46" customHeight="1" spans="1:3">
+    <row r="9" ht="46" customHeight="1" spans="1:6">
       <c r="A9" s="4" t="s">
         <v>26</v>
       </c>
@@ -3222,7 +3223,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" ht="46" customHeight="1" spans="1:5">
+    <row r="10" ht="46" customHeight="1" spans="1:6">
       <c r="A10" s="4"/>
       <c r="B10" s="5" t="s">
         <v>29</v>
@@ -3230,119 +3231,119 @@
       <c r="C10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" ht="46" customHeight="1" spans="1:4">
+    <row r="11" ht="46" customHeight="1" spans="1:6">
       <c r="A11" s="4"/>
       <c r="B11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>33</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" ht="46" customHeight="1" spans="1:3">
+    <row r="12" ht="46" customHeight="1" spans="1:6">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" ht="46" customHeight="1" spans="1:3">
+    <row r="13" ht="46" customHeight="1" spans="1:6">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" ht="46" customHeight="1" spans="1:3">
+    <row r="14" ht="46" customHeight="1" spans="1:6">
       <c r="A14" s="4"/>
       <c r="B14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="15" ht="46" customHeight="1" spans="1:5">
+    <row r="15" ht="46" customHeight="1" spans="1:6">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" ht="82" customHeight="1" spans="1:3">
+    <row r="16" ht="82" customHeight="1" spans="1:6">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" ht="46" customHeight="1" spans="1:3">
+    <row r="17" ht="46" customHeight="1" spans="1:4">
       <c r="A17" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" ht="46" customHeight="1" spans="1:3">
+    <row r="18" ht="46" customHeight="1" spans="1:4">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" ht="46" customHeight="1" spans="1:3">
+    <row r="19" ht="46" customHeight="1" spans="1:4">
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="20" ht="46" customHeight="1" spans="1:3">
+    <row r="20" ht="46" customHeight="1" spans="1:4">
       <c r="A20" s="4"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="21" ht="46" customHeight="1" spans="1:3">
+    <row r="21" ht="46" customHeight="1" spans="1:4">
       <c r="A21" s="4"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="22" ht="46" customHeight="1" spans="1:3">
+    <row r="22" ht="46" customHeight="1" spans="1:4">
       <c r="A22" s="4"/>
       <c r="B22" s="5"/>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="23" ht="46" customHeight="1" spans="1:3">
+    <row r="23" ht="46" customHeight="1" spans="1:4">
       <c r="A23" s="4"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="24" ht="46" customHeight="1" spans="1:3">
+    <row r="24" ht="46" customHeight="1" spans="1:4">
       <c r="A24" s="4"/>
       <c r="B24" s="5"/>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="11" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3358,7 +3359,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" ht="46" customHeight="1" spans="1:3">
+    <row r="26" ht="46" customHeight="1" spans="1:4">
       <c r="A26" s="4"/>
       <c r="B26" s="5" t="s">
         <v>55</v>
@@ -3367,7 +3368,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" ht="46" customHeight="1" spans="1:3">
+    <row r="27" ht="46" customHeight="1" spans="1:4">
       <c r="A27" s="4" t="s">
         <v>57</v>
       </c>
@@ -3378,7 +3379,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" ht="46" customHeight="1" spans="1:3">
+    <row r="28" ht="46" customHeight="1" spans="1:4">
       <c r="A28" s="4"/>
       <c r="B28" s="5" t="s">
         <v>60</v>
@@ -3387,32 +3388,32 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" ht="46" customHeight="1" spans="1:3">
+    <row r="29" ht="46" customHeight="1" spans="1:4">
       <c r="A29" s="4"/>
       <c r="B29" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="13" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="30" ht="46" customHeight="1" spans="1:3">
+    <row r="30" ht="46" customHeight="1" spans="1:4">
       <c r="A30" s="4"/>
       <c r="B30" s="5"/>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="31" ht="46" customHeight="1" spans="1:3">
+    <row r="31" ht="46" customHeight="1" spans="1:4">
       <c r="A31" s="4"/>
       <c r="B31" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="11" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="32" ht="46" customHeight="1" spans="1:3">
+    <row r="32" ht="46" customHeight="1" spans="1:4">
       <c r="A32" s="4" t="s">
         <v>67</v>
       </c>
@@ -3448,21 +3449,21 @@
       <c r="B35" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="11" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="36" ht="46" customHeight="1" spans="1:3">
       <c r="A36" s="4"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="11" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="37" ht="46" customHeight="1" spans="1:3">
       <c r="A37" s="4"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="14" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3475,8 +3476,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39" ht="23.2" spans="1:1">
-      <c r="A39" s="14"/>
+    <row r="39" ht="20.1" spans="1:3">
+      <c r="A39" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="13">
